--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486431_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486431_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1662</v>
+        <v>3.3272</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0469</v>
+        <v>4.1154</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8806</v>
+        <v>-0.7882</v>
       </c>
       <c r="G2" t="n">
         <v>1.9625</v>
@@ -610,13 +610,13 @@
         <v>0.435</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0292</v>
+        <v>0.1902</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1454</v>
+        <v>-0.0769</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1746</v>
+        <v>0.2671</v>
       </c>
       <c r="V2" t="n">
         <v>0.7395</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8746</v>
+        <v>2.3958</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5391</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3355</v>
+        <v>1.4588</v>
       </c>
       <c r="G3" t="n">
         <v>-0.7718</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4714</v>
+        <v>0.9926</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0827</v>
+        <v>0.4807</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3886</v>
+        <v>0.5119</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. RADONCIC</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6568</v>
+        <v>1.8456</v>
       </c>
       <c r="E4" t="n">
-        <v>1.063</v>
+        <v>-0.1076</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5938</v>
+        <v>1.9532</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2432</v>
+        <v>0.0858</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3051</v>
+        <v>-0.3071</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5483</v>
+        <v>0.3928</v>
       </c>
       <c r="J4" t="n">
-        <v>0.91</v>
+        <v>0.325</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4184</v>
+        <v>0.2102</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5084</v>
+        <v>0.1147</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1532</v>
+        <v>-0.2392</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1134</v>
+        <v>-0.5173</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0399</v>
+        <v>0.2781</v>
       </c>
       <c r="P4" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3926</v>
+        <v>2.6101</v>
       </c>
       <c r="S4" t="n">
-        <v>2.725</v>
+        <v>1.3672</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6103</v>
+        <v>0.6549</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1147</v>
+        <v>0.7123</v>
       </c>
       <c r="V4" t="n">
         <v>-1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>J. DIAZ ALEJANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3966</v>
+        <v>1.5178</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2277</v>
+        <v>0.9315</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1689</v>
+        <v>0.5863</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0858</v>
+        <v>0.1043</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3071</v>
+        <v>-0.1674</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3928</v>
+        <v>0.2717</v>
       </c>
       <c r="J5" t="n">
-        <v>0.325</v>
+        <v>1.1706</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2102</v>
+        <v>0.73</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1147</v>
+        <v>0.4407</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2392</v>
+        <v>-1.0663</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5173</v>
+        <v>-0.8974</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2781</v>
+        <v>-0.1689</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6101</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9183</v>
+        <v>1.196</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9902</v>
+        <v>0.8484</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9281</v>
+        <v>0.3476</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. DIAZ ALEJANO</t>
+          <t>D. RADONCIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7606</v>
+        <v>1.5115</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2668</v>
+        <v>0.3492</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4938</v>
+        <v>1.1623</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1043</v>
+        <v>-0.2432</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1674</v>
+        <v>1.3051</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2717</v>
+        <v>-1.5483</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1706</v>
+        <v>0.91</v>
       </c>
       <c r="K6" t="n">
-        <v>0.73</v>
+        <v>2.4184</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4407</v>
+        <v>-1.5084</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0663</v>
+        <v>-1.1532</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8974</v>
+        <v>-1.1134</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1689</v>
+        <v>-0.0399</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4388</v>
+        <v>1.5796</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1837</v>
+        <v>0.8965</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2551</v>
+        <v>0.6832</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. BRNOVIC</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1536</v>
+        <v>1.0898</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5536</v>
+        <v>0.2421</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.8478</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0365</v>
+        <v>-2.3326</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2615</v>
+        <v>-0.468</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.298</v>
+        <v>-1.8646</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4166</v>
+        <v>-1.5308</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3285</v>
+        <v>0.0158</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7451</v>
+        <v>-1.5467</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3801</v>
+        <v>-0.8018</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.067</v>
+        <v>-0.4838</v>
       </c>
       <c r="O7" t="n">
-        <v>0.447</v>
+        <v>-0.318</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>2.1751</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2175</v>
+        <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0274</v>
+        <v>1.2474</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.137</v>
+        <v>0.6429</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1096</v>
+        <v>0.6044</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.8783</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7638</v>
+        <v>-2.1122</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8478</v>
+        <v>2.9905</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.3326</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.468</v>
+        <v>-1.3349</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8646</v>
+        <v>0.404</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5308</v>
+        <v>-1.2566</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0158</v>
+        <v>-0.5531</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5467</v>
+        <v>-0.7036</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8018</v>
+        <v>0.3258</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4838</v>
+        <v>-0.7819</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.318</v>
+        <v>1.1076</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1751</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1751</v>
+        <v>2.3926</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2415</v>
+        <v>1.5917</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3629</v>
+        <v>1.3195</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6044</v>
+        <v>0.2722</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>D. BRNOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.4388</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7395</v>
+        <v>-0.33</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8056</v>
+        <v>0.7688</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.0365</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3349</v>
+        <v>0.2615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.404</v>
+        <v>-0.298</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2566</v>
+        <v>-0.4166</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5531</v>
+        <v>0.3285</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7036</v>
+        <v>-0.7451</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3258</v>
+        <v>0.3801</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7819</v>
+        <v>-0.067</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1076</v>
+        <v>0.447</v>
       </c>
       <c r="P9" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3926</v>
+        <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7794</v>
+        <v>0.2578</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6922</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0872</v>
+        <v>0.1712</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6395</v>
+        <v>-0.1616</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8397</v>
+        <v>1.2867</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4792</v>
+        <v>-1.4484</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4241</v>
@@ -1234,13 +1234,13 @@
         <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1729</v>
+        <v>0.3049</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.3509</v>
       </c>
       <c r="U10" t="n">
-        <v>0.625</v>
+        <v>0.6558</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5649999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.955</v>
+        <v>-1.8557</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4353</v>
+        <v>-4.3668</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4803</v>
+        <v>2.5111</v>
       </c>
       <c r="G11" t="n">
         <v>-4.697</v>
@@ -1312,13 +1312,13 @@
         <v>2.3926</v>
       </c>
       <c r="S11" t="n">
-        <v>1.7642</v>
+        <v>1.8635</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4372</v>
+        <v>1.5057</v>
       </c>
       <c r="U11" t="n">
-        <v>0.327</v>
+        <v>0.3578</v>
       </c>
       <c r="V11" t="n">
         <v>0.7602</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6491</v>
+        <v>-2.73</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6049</v>
+        <v>-1.7167</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0442</v>
+        <v>-1.0133</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4578</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5036</v>
+        <v>0.4227</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1214</v>
+        <v>-0.2331</v>
       </c>
       <c r="U12" t="n">
-        <v>0.625</v>
+        <v>0.6558</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5649999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.9149</v>
+        <v>8.257499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.113899999999999</v>
+        <v>-0.7713999999999994</v>
       </c>
       <c r="F13" t="n">
-        <v>9.028899999999998</v>
+        <v>9.0289</v>
       </c>
       <c r="G13" t="n">
         <v>-11.7413</v>
@@ -1444,7 +1444,7 @@
         <v>-3.7113</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2850999999999992</v>
+        <v>-0.2851000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-3.4264</v>
@@ -1468,13 +1468,13 @@
         <v>19.5757</v>
       </c>
       <c r="S13" t="n">
-        <v>10.6711</v>
+        <v>11.0136</v>
       </c>
       <c r="T13" t="n">
-        <v>5.431699999999999</v>
+        <v>5.7742</v>
       </c>
       <c r="U13" t="n">
-        <v>5.2393</v>
+        <v>5.239300000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8903</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.916</v>
+        <v>3.4016</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3998</v>
+        <v>-0.1763</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3159</v>
+        <v>3.578</v>
       </c>
       <c r="G14" t="n">
         <v>2.708</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5739</v>
+        <v>-0.0883</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0945</v>
+        <v>0.1676</v>
       </c>
       <c r="V14" t="n">
         <v>1.8695</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MARTINEZ CLARIANA</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3863</v>
+        <v>2.8499</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6471</v>
+        <v>0.7674</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2607</v>
+        <v>2.0825</v>
       </c>
       <c r="G15" t="n">
-        <v>3.777</v>
+        <v>1.8527</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9889</v>
+        <v>1.0431</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7881</v>
+        <v>0.8096</v>
       </c>
       <c r="J15" t="n">
-        <v>3.178</v>
+        <v>0.1674</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2655</v>
+        <v>0.1674</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9125</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.599</v>
+        <v>1.6853</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.8757</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1243</v>
+        <v>0.8096</v>
       </c>
       <c r="P15" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-0.2175</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.305</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6082</v>
+        <v>-0.3725</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2091</v>
+        <v>-0.3124</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8173</v>
+        <v>-0.0601</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.9347</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>A. MARTINEZ CLARIANA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8095</v>
+        <v>2.2065</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5439000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="F16" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.9889</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.7881</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.178</v>
+      </c>
+      <c r="K16" t="n">
         <v>1.2655</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.8527</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.0431</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.8096</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.1674</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.1674</v>
-      </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.9125</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6853</v>
+        <v>0.599</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8757</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8096</v>
+        <v>-0.1243</v>
       </c>
       <c r="P16" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.413</v>
+        <v>-0.788</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.536</v>
+        <v>-0.2379</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.877</v>
+        <v>-0.5501</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9347</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4936</v>
+        <v>1.5387</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0635</v>
+        <v>1.1752</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4302</v>
+        <v>0.3634</v>
       </c>
       <c r="G17" t="n">
         <v>3.8353</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3395</v>
+        <v>-1.2945</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-0.5843</v>
       </c>
       <c r="V17" t="n">
         <v>0.9554</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0059</v>
+        <v>0.6007</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.4584</v>
       </c>
       <c r="F18" t="n">
-        <v>0.576</v>
+        <v>1.059</v>
       </c>
       <c r="G18" t="n">
         <v>1.1813</v>
@@ -1858,13 +1858,13 @@
         <v>0.87</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0003</v>
+        <v>-0.4056</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6165</v>
+        <v>-0.5047</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3838</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>1.13</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6102</v>
+        <v>-0.6116</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8112</v>
+        <v>-1.1465</v>
       </c>
       <c r="F19" t="n">
-        <v>0.201</v>
+        <v>0.5349</v>
       </c>
       <c r="G19" t="n">
         <v>0.6019</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5172</v>
+        <v>-0.5185</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0601</v>
+        <v>-0.2752</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5773</v>
+        <v>-0.2434</v>
       </c>
       <c r="V19" t="n">
         <v>-1.13</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9723</v>
+        <v>-2.0763</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.4875</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.373</v>
+        <v>-1.5888</v>
       </c>
       <c r="G20" t="n">
         <v>2.023</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.8595</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6044</v>
+        <v>-0.4927</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1511</v>
+        <v>-0.3668</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4997</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9098</v>
+        <v>-2.5758</v>
       </c>
       <c r="E21" t="n">
         <v>-1.4758</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.434</v>
+        <v>-1.1001</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1991</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1457</v>
+        <v>-0.8117</v>
       </c>
       <c r="T21" t="n">
         <v>-0.822</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3237</v>
+        <v>0.0102</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2048</v>
+        <v>-3.0673</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0086</v>
+        <v>0.1204</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2134</v>
+        <v>-3.1877</v>
       </c>
       <c r="G22" t="n">
         <v>1.173</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5278</v>
+        <v>-1.3904</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9469</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5809</v>
+        <v>-0.5552</v>
       </c>
       <c r="V22" t="n">
         <v>0.1952</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7729</v>
+        <v>-3.3438</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4739</v>
+        <v>-4.2504</v>
       </c>
       <c r="F23" t="n">
-        <v>0.701</v>
+        <v>0.9066</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1356</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2898</v>
+        <v>-0.8607</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.536</v>
+        <v>-0.3124</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7538</v>
+        <v>-0.5483</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0564</v>
+        <v>-3.8572</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.9619</v>
+        <v>-5.2972</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9056</v>
+        <v>1.44</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0761</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5001</v>
+        <v>-0.301</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1454</v>
+        <v>-0.4807</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3548</v>
+        <v>0.1796</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.915100000000001</v>
+        <v>-4.9346</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.0289</v>
+        <v>-9.0291</v>
       </c>
       <c r="F25" t="n">
-        <v>1.114099999999999</v>
+        <v>4.0943</v>
       </c>
       <c r="G25" t="n">
         <v>11.7414</v>
@@ -2374,7 +2374,7 @@
         <v>9.183399999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.558000000000001</v>
+        <v>2.558</v>
       </c>
       <c r="J25" t="n">
         <v>8.029999999999998</v>
@@ -2386,7 +2386,7 @@
         <v>-0.8685999999999992</v>
       </c>
       <c r="M25" t="n">
-        <v>3.711399999999999</v>
+        <v>3.7114</v>
       </c>
       <c r="N25" t="n">
         <v>0.2850000000000005</v>
@@ -2404,13 +2404,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.671</v>
+        <v>-7.6907</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.239500000000001</v>
+        <v>-5.2394</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.4318</v>
+        <v>-2.4517</v>
       </c>
       <c r="V25" t="n">
         <v>1.8901</v>
